--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_OLYMPIACOS PIRAEUS.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_OLYMPIACOS PIRAEUS.xlsx
@@ -565,13 +565,13 @@
         <v>35</v>
       </c>
       <c r="D2" t="n">
-        <v>164.6979</v>
+        <v>118.3725</v>
       </c>
       <c r="E2" t="n">
-        <v>138.5736</v>
+        <v>99.2557</v>
       </c>
       <c r="F2" t="n">
-        <v>26.1241</v>
+        <v>19.1166</v>
       </c>
       <c r="G2" t="n">
         <v>22.3096</v>
@@ -610,13 +610,13 @@
         <v>52.6534</v>
       </c>
       <c r="S2" t="n">
-        <v>80.8501</v>
+        <v>34.5249</v>
       </c>
       <c r="T2" t="n">
-        <v>61.9294</v>
+        <v>22.6117</v>
       </c>
       <c r="U2" t="n">
-        <v>18.921</v>
+        <v>11.913</v>
       </c>
       <c r="V2" t="n">
         <v>42.2859</v>
@@ -643,13 +643,13 @@
         <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>116.5131</v>
+        <v>108.4424</v>
       </c>
       <c r="E3" t="n">
-        <v>80.98560000000001</v>
+        <v>81.05200000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>35.5274</v>
+        <v>27.3906</v>
       </c>
       <c r="G3" t="n">
         <v>1.548199999999999</v>
@@ -688,13 +688,13 @@
         <v>67.26609999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>27.2879</v>
+        <v>19.2173</v>
       </c>
       <c r="T3" t="n">
-        <v>9.388399999999999</v>
+        <v>9.454600000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>17.8999</v>
+        <v>9.7629</v>
       </c>
       <c r="V3" t="n">
         <v>66.5697</v>
@@ -721,13 +721,13 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>82.9502</v>
+        <v>59.2494</v>
       </c>
       <c r="E4" t="n">
-        <v>76.52070000000001</v>
+        <v>56.4647</v>
       </c>
       <c r="F4" t="n">
-        <v>6.4293</v>
+        <v>2.784899999999999</v>
       </c>
       <c r="G4" t="n">
         <v>24.8222</v>
@@ -766,13 +766,13 @@
         <v>35.9533</v>
       </c>
       <c r="S4" t="n">
-        <v>37.2904</v>
+        <v>13.59</v>
       </c>
       <c r="T4" t="n">
-        <v>28.9942</v>
+        <v>8.9384</v>
       </c>
       <c r="U4" t="n">
-        <v>8.295999999999999</v>
+        <v>4.6514</v>
       </c>
       <c r="V4" t="n">
         <v>7.616199999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D5" t="n">
-        <v>26.2898</v>
+        <v>47.2705</v>
       </c>
       <c r="E5" t="n">
-        <v>24.3932</v>
+        <v>35.1295</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8965</v>
+        <v>12.1412</v>
       </c>
       <c r="G5" t="n">
-        <v>12.6157</v>
+        <v>27.6966</v>
       </c>
       <c r="H5" t="n">
-        <v>10.1422</v>
+        <v>5.4867</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4736</v>
+        <v>22.21</v>
       </c>
       <c r="J5" t="n">
-        <v>17.3123</v>
+        <v>69.631</v>
       </c>
       <c r="K5" t="n">
-        <v>11.6443</v>
+        <v>27.4378</v>
       </c>
       <c r="L5" t="n">
-        <v>5.6678</v>
+        <v>42.1929</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.6967</v>
+        <v>-41.9348</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5022</v>
+        <v>-21.9508</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.1943</v>
+        <v>-19.9838</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7834</v>
+        <v>-23.1952</v>
       </c>
       <c r="Q5" t="n">
-        <v>-15.7727</v>
+        <v>-92.31740000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>18.5563</v>
+        <v>69.122</v>
       </c>
       <c r="S5" t="n">
-        <v>14.865</v>
+        <v>9.5176</v>
       </c>
       <c r="T5" t="n">
-        <v>12.969</v>
+        <v>4.7761</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8961</v>
+        <v>4.741099999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.9742</v>
+        <v>33.2519</v>
       </c>
       <c r="W5" t="n">
-        <v>9.8848</v>
+        <v>53.0391</v>
       </c>
       <c r="X5" t="n">
-        <v>-13.859</v>
+        <v>-19.7872</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>16.0919</v>
+        <v>18.1887</v>
       </c>
       <c r="E6" t="n">
-        <v>14.8501</v>
+        <v>16.6712</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2419</v>
+        <v>1.517299999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>27.6966</v>
+        <v>12.6157</v>
       </c>
       <c r="H6" t="n">
-        <v>5.4867</v>
+        <v>10.1422</v>
       </c>
       <c r="I6" t="n">
-        <v>22.21</v>
+        <v>2.4736</v>
       </c>
       <c r="J6" t="n">
-        <v>69.631</v>
+        <v>17.3123</v>
       </c>
       <c r="K6" t="n">
-        <v>27.4378</v>
+        <v>11.6443</v>
       </c>
       <c r="L6" t="n">
-        <v>42.1929</v>
+        <v>5.6678</v>
       </c>
       <c r="M6" t="n">
-        <v>-41.9348</v>
+        <v>-4.6967</v>
       </c>
       <c r="N6" t="n">
-        <v>-21.9508</v>
+        <v>-1.5022</v>
       </c>
       <c r="O6" t="n">
-        <v>-19.9838</v>
+        <v>-3.1943</v>
       </c>
       <c r="P6" t="n">
-        <v>-23.1952</v>
+        <v>2.7834</v>
       </c>
       <c r="Q6" t="n">
-        <v>-92.31740000000001</v>
+        <v>-15.7727</v>
       </c>
       <c r="R6" t="n">
-        <v>69.122</v>
+        <v>18.5563</v>
       </c>
       <c r="S6" t="n">
-        <v>-21.6613</v>
+        <v>6.7639</v>
       </c>
       <c r="T6" t="n">
-        <v>-15.5032</v>
+        <v>5.247</v>
       </c>
       <c r="U6" t="n">
-        <v>-6.1579</v>
+        <v>1.5168</v>
       </c>
       <c r="V6" t="n">
-        <v>33.2519</v>
+        <v>-3.9742</v>
       </c>
       <c r="W6" t="n">
-        <v>53.0391</v>
+        <v>9.8848</v>
       </c>
       <c r="X6" t="n">
-        <v>-19.7872</v>
+        <v>-13.859</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>6.6608</v>
+        <v>11.737</v>
       </c>
       <c r="E7" t="n">
-        <v>8.875399999999999</v>
+        <v>0.1531999999999989</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2149</v>
+        <v>11.5842</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2393</v>
+        <v>16.3641</v>
       </c>
       <c r="H7" t="n">
-        <v>4.028500000000001</v>
+        <v>11.7294</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2104999999999995</v>
+        <v>4.635</v>
       </c>
       <c r="J7" t="n">
-        <v>26.0229</v>
+        <v>50.5324</v>
       </c>
       <c r="K7" t="n">
-        <v>16.7011</v>
+        <v>27.0675</v>
       </c>
       <c r="L7" t="n">
-        <v>9.322100000000001</v>
+        <v>23.4648</v>
       </c>
       <c r="M7" t="n">
-        <v>-21.7833</v>
+        <v>-34.1684</v>
       </c>
       <c r="N7" t="n">
-        <v>-12.6721</v>
+        <v>-15.3385</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.1112</v>
+        <v>-18.8301</v>
       </c>
       <c r="P7" t="n">
-        <v>1.159699999999999</v>
+        <v>-0.0002000000000004221</v>
       </c>
       <c r="Q7" t="n">
-        <v>-39.4319</v>
+        <v>-58.9161</v>
       </c>
       <c r="R7" t="n">
-        <v>40.5921</v>
+        <v>58.9161</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5787</v>
+        <v>6.551299999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2555</v>
+        <v>2.4658</v>
       </c>
       <c r="U7" t="n">
-        <v>4.8344</v>
+        <v>4.0852</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.3173</v>
+        <v>-11.1785</v>
       </c>
       <c r="W7" t="n">
-        <v>23.5399</v>
+        <v>6.07</v>
       </c>
       <c r="X7" t="n">
-        <v>-25.8572</v>
+        <v>-17.2485</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7812</v>
+        <v>11.5024</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6675</v>
+        <v>13.1056</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8863</v>
+        <v>-1.6032</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1521</v>
+        <v>4.2393</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2629</v>
+        <v>4.028500000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1108</v>
+        <v>0.2104999999999995</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7852</v>
+        <v>26.0229</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1596</v>
+        <v>16.7011</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6257</v>
+        <v>9.322100000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6331</v>
+        <v>-21.7833</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1034</v>
+        <v>-12.6721</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7365</v>
+        <v>-9.1112</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.232</v>
+        <v>1.159699999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.232</v>
+        <v>-39.4319</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>40.5921</v>
       </c>
       <c r="S8" t="n">
-        <v>0.861</v>
+        <v>8.420300000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1142</v>
+        <v>2.9747</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7468</v>
+        <v>5.4458</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.3173</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>23.5399</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-25.8572</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. EVANS</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3383</v>
+        <v>7.9011</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0211</v>
+        <v>-1.5769</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3593</v>
+        <v>9.478100000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6827</v>
+        <v>-8.921099999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0168</v>
+        <v>5.2721</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6659</v>
+        <v>-14.1931</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0536</v>
+        <v>16.7372</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0168</v>
+        <v>18.8582</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0368</v>
+        <v>-2.1207</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6291</v>
+        <v>-25.6583</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-13.5862</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6291</v>
+        <v>-12.0722</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>5.7989</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-42.2158</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>48.01439999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3444</v>
+        <v>8.533100000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0747</v>
+        <v>4.1623</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2697</v>
+        <v>4.3706</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.490100000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>19.7386</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-17.2485</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>S. MCKISSIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.03950000000000042</v>
+        <v>3.248399999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.8439</v>
+        <v>1.3806</v>
       </c>
       <c r="F10" t="n">
-        <v>7.804399999999999</v>
+        <v>1.8675</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.921099999999999</v>
+        <v>-5.6095</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2721</v>
+        <v>3.2441</v>
       </c>
       <c r="I10" t="n">
-        <v>-14.1931</v>
+        <v>-8.853299999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>16.7372</v>
+        <v>6.9437</v>
       </c>
       <c r="K10" t="n">
-        <v>18.8582</v>
+        <v>8.333500000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1207</v>
+        <v>-1.389900000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-25.6583</v>
+        <v>-12.5534</v>
       </c>
       <c r="N10" t="n">
-        <v>-13.5862</v>
+        <v>-5.0895</v>
       </c>
       <c r="O10" t="n">
-        <v>-12.0722</v>
+        <v>-7.4632</v>
       </c>
       <c r="P10" t="n">
-        <v>5.7989</v>
+        <v>6.9588</v>
       </c>
       <c r="Q10" t="n">
-        <v>-42.2158</v>
+        <v>-12.2939</v>
       </c>
       <c r="R10" t="n">
-        <v>48.01439999999999</v>
+        <v>19.2524</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5925999999999999</v>
+        <v>0.7341000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.1046</v>
+        <v>-0.2214</v>
       </c>
       <c r="U10" t="n">
-        <v>2.6971</v>
+        <v>0.9553</v>
       </c>
       <c r="V10" t="n">
-        <v>2.490100000000001</v>
+        <v>1.1655</v>
       </c>
       <c r="W10" t="n">
-        <v>19.7386</v>
+        <v>6.9519</v>
       </c>
       <c r="X10" t="n">
-        <v>-17.2485</v>
+        <v>-5.7864</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. ANTETOKOUNMPO</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3927</v>
+        <v>0.8990999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5958</v>
+        <v>1.7854</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9887</v>
+        <v>-0.8863</v>
       </c>
       <c r="G11" t="n">
-        <v>3.0126</v>
+        <v>0.1521</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6204</v>
+        <v>1.2629</v>
       </c>
       <c r="I11" t="n">
-        <v>1.392</v>
+        <v>-1.1108</v>
       </c>
       <c r="J11" t="n">
-        <v>2.3801</v>
+        <v>1.7852</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7177</v>
+        <v>1.1596</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6625000000000001</v>
+        <v>0.6257</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6325000000000001</v>
+        <v>-1.6331</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.09700000000000003</v>
+        <v>0.1034</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7295</v>
+        <v>-1.7365</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9277</v>
+        <v>-0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.6237</v>
+        <v>-0.232</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6960000000000001</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6694</v>
+        <v>0.9790000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6281</v>
+        <v>0.2321</v>
       </c>
       <c r="U11" t="n">
-        <v>0.04130000000000011</v>
+        <v>0.7468</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.147</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.3584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. NETZIPOGLOU</t>
+          <t>K. EVANS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7477</v>
+        <v>0.4055</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6184</v>
+        <v>-0.0211</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1293</v>
+        <v>0.4266</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1442</v>
+        <v>0.6827</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0769</v>
+        <v>0.0168</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0673</v>
+        <v>0.6659</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4364</v>
+        <v>0.0536</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.6868</v>
+        <v>0.0168</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7077</v>
+        <v>0.6291</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3899</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3178</v>
+        <v>0.6291</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1466</v>
+        <v>-0.2772</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0499</v>
+        <v>-0.0747</v>
       </c>
       <c r="U12" t="n">
-        <v>0.09660000000000001</v>
+        <v>-0.2025</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. MCKISSIC</t>
+          <t>C. JOSEPH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.836599999999999</v>
+        <v>0.2366999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3385</v>
+        <v>0.3366</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4982</v>
+        <v>-0.1001000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.6095</v>
+        <v>0.8631000000000003</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2441</v>
+        <v>2.2582</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.853299999999999</v>
+        <v>-1.3953</v>
       </c>
       <c r="J13" t="n">
-        <v>6.9437</v>
+        <v>7.8006</v>
       </c>
       <c r="K13" t="n">
-        <v>8.333500000000001</v>
+        <v>6.2121</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.389900000000001</v>
+        <v>1.5883</v>
       </c>
       <c r="M13" t="n">
-        <v>-12.5534</v>
+        <v>-6.9376</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.0895</v>
+        <v>-3.954</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.4632</v>
+        <v>-2.9836</v>
       </c>
       <c r="P13" t="n">
-        <v>6.9588</v>
+        <v>-3.4793</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.2939</v>
+        <v>-15.3089</v>
       </c>
       <c r="R13" t="n">
-        <v>19.2524</v>
+        <v>11.8298</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.3512</v>
+        <v>2.9948</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.9407</v>
+        <v>1.775</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.4107</v>
+        <v>1.2197</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1655</v>
+        <v>-0.1418000000000005</v>
       </c>
       <c r="W13" t="n">
-        <v>6.9519</v>
+        <v>6.07</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.7864</v>
+        <v>-6.2118</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. JOSEPH</t>
+          <t>K. ANTETOKOUNMPO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.797899999999999</v>
+        <v>-1.5216</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.8925</v>
+        <v>0.5343</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9052</v>
+        <v>-2.0559</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8631000000000003</v>
+        <v>3.0126</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2582</v>
+        <v>1.6204</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.3953</v>
+        <v>1.392</v>
       </c>
       <c r="J14" t="n">
-        <v>7.8006</v>
+        <v>2.3801</v>
       </c>
       <c r="K14" t="n">
-        <v>6.2121</v>
+        <v>1.7177</v>
       </c>
       <c r="L14" t="n">
-        <v>1.5883</v>
+        <v>0.6625000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.9376</v>
+        <v>0.6325000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.954</v>
+        <v>-0.09700000000000003</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.9836</v>
+        <v>0.7295</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.4793</v>
+        <v>-0.9277</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.3089</v>
+        <v>-1.6237</v>
       </c>
       <c r="R14" t="n">
-        <v>11.8298</v>
+        <v>0.6960000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0397</v>
+        <v>0.5405000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4544000000000001</v>
+        <v>0.5665</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5857</v>
+        <v>-0.02590000000000003</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1418000000000005</v>
+        <v>-4.147</v>
       </c>
       <c r="W14" t="n">
-        <v>6.07</v>
+        <v>-0.7886</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.2118</v>
+        <v>-3.3584</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>O. NETZIPOGLOU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.164099999999999</v>
+        <v>-3.1119</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.4598</v>
+        <v>-2.2514</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2959</v>
+        <v>-0.8603999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>16.3641</v>
+        <v>-3.1442</v>
       </c>
       <c r="H15" t="n">
-        <v>11.7294</v>
+        <v>-2.0769</v>
       </c>
       <c r="I15" t="n">
-        <v>4.635</v>
+        <v>-1.0673</v>
       </c>
       <c r="J15" t="n">
-        <v>50.5324</v>
+        <v>-2.4364</v>
       </c>
       <c r="K15" t="n">
-        <v>27.0675</v>
+        <v>-1.6868</v>
       </c>
       <c r="L15" t="n">
-        <v>23.4648</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-34.1684</v>
+        <v>-0.7077</v>
       </c>
       <c r="N15" t="n">
-        <v>-15.3385</v>
+        <v>-0.3899</v>
       </c>
       <c r="O15" t="n">
-        <v>-18.8301</v>
+        <v>-0.3178</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.0002000000000004221</v>
+        <v>0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>-58.9161</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>58.9161</v>
+        <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>-10.3497</v>
+        <v>0.7824</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.1468</v>
+        <v>0.4168000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.203</v>
+        <v>0.3655</v>
       </c>
       <c r="V15" t="n">
-        <v>-11.1785</v>
+        <v>-1.214</v>
       </c>
       <c r="W15" t="n">
-        <v>6.07</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-17.2485</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>-6.3575</v>
+        <v>-5.280099999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.2254</v>
+        <v>-3.5177</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.132</v>
+        <v>-1.7625</v>
       </c>
       <c r="G16" t="n">
         <v>-2.0838</v>
@@ -1702,13 +1702,13 @@
         <v>0.464</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9721</v>
+        <v>0.1052</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9630000000000001</v>
+        <v>-0.2553</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.009300000000000003</v>
+        <v>0.3605</v>
       </c>
       <c r="V16" t="n">
         <v>-1.214</v>
@@ -1735,13 +1735,13 @@
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>-13.92</v>
+        <v>-11.3354</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.5838</v>
+        <v>-6.7399</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.336</v>
+        <v>-4.5957</v>
       </c>
       <c r="G17" t="n">
         <v>-11.4984</v>
@@ -1780,13 +1780,13 @@
         <v>4.4071</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0789</v>
+        <v>1.5058</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0763</v>
+        <v>0.7675999999999998</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.002700000000000022</v>
+        <v>0.738</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6468</v>
@@ -1813,13 +1813,13 @@
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>-19.5793</v>
+        <v>-14.2234</v>
       </c>
       <c r="E18" t="n">
-        <v>-13.2473</v>
+        <v>-9.7521</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.332100000000001</v>
+        <v>-4.4718</v>
       </c>
       <c r="G18" t="n">
         <v>-2.2791</v>
@@ -1858,13 +1858,13 @@
         <v>7.1906</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.8109</v>
+        <v>-2.455</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.8069</v>
+        <v>-1.3116</v>
       </c>
       <c r="U18" t="n">
-        <v>-3.0038</v>
+        <v>-1.1434</v>
       </c>
       <c r="V18" t="n">
         <v>0.2524999999999999</v>
@@ -1891,13 +1891,13 @@
         <v>23</v>
       </c>
       <c r="D19" t="n">
-        <v>-28.9298</v>
+        <v>-17.5</v>
       </c>
       <c r="E19" t="n">
-        <v>-21.0514</v>
+        <v>-14.9338</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.8786</v>
+        <v>-2.5661</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1268</v>
@@ -1936,13 +1936,13 @@
         <v>27.1386</v>
       </c>
       <c r="S19" t="n">
-        <v>-10.7954</v>
+        <v>0.6348</v>
       </c>
       <c r="T19" t="n">
-        <v>-2.3355</v>
+        <v>3.7819</v>
       </c>
       <c r="U19" t="n">
-        <v>-8.4598</v>
+        <v>-3.1476</v>
       </c>
       <c r="V19" t="n">
         <v>-7.425800000000001</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D20" t="n">
-        <v>-38.0642</v>
+        <v>-18.7004</v>
       </c>
       <c r="E20" t="n">
-        <v>-36.1726</v>
+        <v>-20.9886</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.892</v>
+        <v>2.2878</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.601199999999999</v>
+        <v>-15.0971</v>
       </c>
       <c r="H20" t="n">
-        <v>3.7286</v>
+        <v>-4.383599999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-10.3295</v>
+        <v>-10.7135</v>
       </c>
       <c r="J20" t="n">
-        <v>11.1286</v>
+        <v>18.7859</v>
       </c>
       <c r="K20" t="n">
-        <v>11.0077</v>
+        <v>8.360199999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1206999999999997</v>
+        <v>10.4251</v>
       </c>
       <c r="M20" t="n">
-        <v>-17.7296</v>
+        <v>-33.8829</v>
       </c>
       <c r="N20" t="n">
-        <v>-7.2796</v>
+        <v>-12.7438</v>
       </c>
       <c r="O20" t="n">
-        <v>-10.4505</v>
+        <v>-21.139</v>
       </c>
       <c r="P20" t="n">
-        <v>-8.814200000000001</v>
+        <v>-11.8296</v>
       </c>
       <c r="Q20" t="n">
-        <v>-38.0406</v>
+        <v>-67.2663</v>
       </c>
       <c r="R20" t="n">
-        <v>29.2265</v>
+        <v>55.4369</v>
       </c>
       <c r="S20" t="n">
-        <v>-8.032400000000001</v>
+        <v>2.6435</v>
       </c>
       <c r="T20" t="n">
-        <v>-8.361700000000001</v>
+        <v>3.6683</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3293000000000001</v>
+        <v>-1.0247</v>
       </c>
       <c r="V20" t="n">
-        <v>-14.6165</v>
+        <v>5.582400000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.8992999999999999</v>
+        <v>23.8235</v>
       </c>
       <c r="X20" t="n">
-        <v>-13.7172</v>
+        <v>-18.2411</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,70 +2044,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D21" t="n">
-        <v>-43.1343</v>
+        <v>-27.8162</v>
       </c>
       <c r="E21" t="n">
-        <v>-36.4753</v>
+        <v>-28.1126</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.6595</v>
+        <v>0.2966000000000002</v>
       </c>
       <c r="G21" t="n">
-        <v>-15.0971</v>
+        <v>-6.601199999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.383599999999999</v>
+        <v>3.7286</v>
       </c>
       <c r="I21" t="n">
-        <v>-10.7135</v>
+        <v>-10.3295</v>
       </c>
       <c r="J21" t="n">
-        <v>18.7859</v>
+        <v>11.1286</v>
       </c>
       <c r="K21" t="n">
-        <v>8.360199999999999</v>
+        <v>11.0077</v>
       </c>
       <c r="L21" t="n">
-        <v>10.4251</v>
+        <v>0.1206999999999997</v>
       </c>
       <c r="M21" t="n">
-        <v>-33.8829</v>
+        <v>-17.7296</v>
       </c>
       <c r="N21" t="n">
-        <v>-12.7438</v>
+        <v>-7.2796</v>
       </c>
       <c r="O21" t="n">
-        <v>-21.139</v>
+        <v>-10.4505</v>
       </c>
       <c r="P21" t="n">
-        <v>-11.8296</v>
+        <v>-8.814200000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-67.2663</v>
+        <v>-38.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>55.4369</v>
+        <v>29.2265</v>
       </c>
       <c r="S21" t="n">
-        <v>-21.7902</v>
+        <v>2.2157</v>
       </c>
       <c r="T21" t="n">
-        <v>-11.8183</v>
+        <v>-0.3019000000000002</v>
       </c>
       <c r="U21" t="n">
-        <v>-9.9717</v>
+        <v>2.5177</v>
       </c>
       <c r="V21" t="n">
-        <v>5.582400000000001</v>
+        <v>-14.6165</v>
       </c>
       <c r="W21" t="n">
-        <v>23.8235</v>
+        <v>-0.8992999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>-18.2411</v>
+        <v>-13.7172</v>
       </c>
     </row>
     <row r="22">
@@ -2125,19 +2125,19 @@
         <v>38</v>
       </c>
       <c r="D22" t="n">
-        <v>249.3595999999999</v>
+        <v>287.9647</v>
       </c>
       <c r="E22" t="n">
-        <v>204.5319</v>
+        <v>217.9747</v>
       </c>
       <c r="F22" t="n">
-        <v>44.826</v>
+        <v>69.9894</v>
       </c>
       <c r="G22" t="n">
-        <v>56.94500000000001</v>
+        <v>56.945</v>
       </c>
       <c r="H22" t="n">
-        <v>93.26479999999998</v>
+        <v>93.26480000000001</v>
       </c>
       <c r="I22" t="n">
         <v>-36.31859999999999</v>
@@ -2161,7 +2161,7 @@
         <v>-177.2437</v>
       </c>
       <c r="P22" t="n">
-        <v>1.160100000000005</v>
+        <v>1.160099999999998</v>
       </c>
       <c r="Q22" t="n">
         <v>-546.252</v>
@@ -2170,13 +2170,13 @@
         <v>547.4115</v>
       </c>
       <c r="S22" t="n">
-        <v>78.91549999999999</v>
+        <v>117.522</v>
       </c>
       <c r="T22" t="n">
-        <v>56.23160000000001</v>
+        <v>69.67389999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>22.6842</v>
+        <v>47.8462</v>
       </c>
       <c r="V22" t="n">
         <v>112.3383</v>
